--- a/notebooks/rda-experiments/runs/v9-sample3/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v9-sample3/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="124">
   <si>
     <t>fields in reference</t>
   </si>
@@ -383,7 +383,10 @@
     <t>planned</t>
   </si>
   <si>
-    <t>only 50% of the model's words are in the reference</t>
+    <t>only 40% of the model's words are in the reference</t>
+  </si>
+  <si>
+    <t>only 38% of the model's words are in the reference</t>
   </si>
   <si>
     <t>only 14% of the model's words are in the reference</t>
@@ -872,31 +875,31 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>0.763</v>
+        <v>0.711</v>
       </c>
       <c r="H4">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>0.589</v>
+        <v>0.512</v>
       </c>
       <c r="J4">
-        <v>0.5686274509803921</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="K4">
-        <v>0.1764705882352941</v>
+        <v>0.2075471698113208</v>
       </c>
       <c r="L4">
-        <v>0.2549019607843137</v>
+        <v>0.2830188679245283</v>
       </c>
     </row>
   </sheetData>
@@ -2649,7 +2652,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2768,7 +2771,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -2785,7 +2788,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -2802,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -2822,7 +2825,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
@@ -2842,7 +2845,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -2851,13 +2854,10 @@
         <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
@@ -2874,10 +2874,13 @@
         <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="G12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2885,7 +2888,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
@@ -2902,7 +2905,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
@@ -2919,7 +2922,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
@@ -2939,7 +2942,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
@@ -2959,7 +2962,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
@@ -2968,10 +2971,13 @@
         <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="G17" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2979,7 +2985,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
         <v>58</v>
@@ -2988,10 +2994,13 @@
         <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="G18" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3242,7 +3251,7 @@
         <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3395,10 +3404,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
         <v>97</v>
@@ -3409,10 +3418,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
         <v>97</v>
@@ -3423,10 +3432,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F42" t="s">
         <v>97</v>
@@ -3437,10 +3446,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E43" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
         <v>97</v>
@@ -3451,10 +3460,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
         <v>97</v>
@@ -3465,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F45" t="s">
         <v>97</v>
@@ -3479,10 +3488,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s">
         <v>97</v>
@@ -3493,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
         <v>97</v>
@@ -3507,7 +3516,7 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E48" t="s">
         <v>78</v>
@@ -3521,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
         <v>97</v>
@@ -3535,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E50" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F50" t="s">
         <v>97</v>
@@ -3549,10 +3558,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F51" t="s">
         <v>97</v>
@@ -3563,12 +3572,40 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
         <v>70</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E54" t="s">
         <v>94</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F54" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3579,7 +3616,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -5684,7 +5721,7 @@
         <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D103" t="s">
         <v>27</v>
@@ -5704,7 +5741,7 @@
         <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D104" t="s">
         <v>28</v>
@@ -5724,7 +5761,7 @@
         <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D105" t="s">
         <v>29</v>
@@ -5747,7 +5784,7 @@
         <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s">
         <v>30</v>
@@ -5770,7 +5807,7 @@
         <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D107" t="s">
         <v>31</v>
@@ -5779,13 +5816,10 @@
         <v>114</v>
       </c>
       <c r="F107" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G107" t="s">
-        <v>96</v>
-      </c>
-      <c r="H107" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -5796,7 +5830,7 @@
         <v>14</v>
       </c>
       <c r="C108" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D108" t="s">
         <v>56</v>
@@ -5805,10 +5839,13 @@
         <v>115</v>
       </c>
       <c r="F108" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G108" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="H108" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -5819,7 +5856,7 @@
         <v>14</v>
       </c>
       <c r="C109" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D109" t="s">
         <v>33</v>
@@ -5839,7 +5876,7 @@
         <v>14</v>
       </c>
       <c r="C110" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D110" t="s">
         <v>34</v>
@@ -5859,7 +5896,7 @@
         <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D111" t="s">
         <v>35</v>
@@ -5882,7 +5919,7 @@
         <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D112" t="s">
         <v>36</v>
@@ -5905,7 +5942,7 @@
         <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D113" t="s">
         <v>37</v>
@@ -5914,10 +5951,13 @@
         <v>116</v>
       </c>
       <c r="F113" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G113" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="H113" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -5928,7 +5968,7 @@
         <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D114" t="s">
         <v>58</v>
@@ -5937,10 +5977,13 @@
         <v>117</v>
       </c>
       <c r="F114" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G114" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="H114" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6230,7 +6273,7 @@
         <v>96</v>
       </c>
       <c r="H127" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -6410,10 +6453,10 @@
         <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G136" t="s">
         <v>97</v>
@@ -6427,10 +6470,10 @@
         <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F137" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G137" t="s">
         <v>97</v>
@@ -6444,10 +6487,10 @@
         <v>14</v>
       </c>
       <c r="C138" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F138" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G138" t="s">
         <v>97</v>
@@ -6461,10 +6504,10 @@
         <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F139" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G139" t="s">
         <v>97</v>
@@ -6478,10 +6521,10 @@
         <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F140" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G140" t="s">
         <v>97</v>
@@ -6495,10 +6538,10 @@
         <v>14</v>
       </c>
       <c r="C141" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F141" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G141" t="s">
         <v>97</v>
@@ -6512,10 +6555,10 @@
         <v>14</v>
       </c>
       <c r="C142" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F142" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G142" t="s">
         <v>97</v>
@@ -6529,10 +6572,10 @@
         <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F143" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G143" t="s">
         <v>97</v>
@@ -6546,7 +6589,7 @@
         <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F144" t="s">
         <v>78</v>
@@ -6563,10 +6606,10 @@
         <v>14</v>
       </c>
       <c r="C145" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F145" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="G145" t="s">
         <v>97</v>
@@ -6580,10 +6623,10 @@
         <v>14</v>
       </c>
       <c r="C146" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F146" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G146" t="s">
         <v>97</v>
@@ -6597,10 +6640,10 @@
         <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F147" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="G147" t="s">
         <v>97</v>
@@ -6614,12 +6657,46 @@
         <v>14</v>
       </c>
       <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="F148" t="s">
+        <v>72</v>
+      </c>
+      <c r="G148" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149">
+        <v>3</v>
+      </c>
+      <c r="B149" t="s">
+        <v>14</v>
+      </c>
+      <c r="C149" t="s">
+        <v>69</v>
+      </c>
+      <c r="F149" t="s">
+        <v>93</v>
+      </c>
+      <c r="G149" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150">
+        <v>3</v>
+      </c>
+      <c r="B150" t="s">
+        <v>14</v>
+      </c>
+      <c r="C150" t="s">
         <v>70</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F150" t="s">
         <v>94</v>
       </c>
-      <c r="G148" t="s">
+      <c r="G150" t="s">
         <v>97</v>
       </c>
     </row>
